--- a/birimler.xlsx
+++ b/birimler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BA05C3-2DCC-4DC0-BE92-DD7A33B8BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0F144A-02A0-4ADA-A95F-3075F3ED05BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{E900B2A5-0F99-4661-87B7-C6F096001B9C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{E900B2A5-0F99-4661-87B7-C6F096001B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="AKDENİZ" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
     <t>Tolköy</t>
   </si>
   <si>
-    <t>Volkan İZCİ</t>
+    <t>Burak AKBAŞ</t>
   </si>
 </sst>
 </file>
@@ -1635,37 +1635,37 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
